--- a/A/chrII:526178-574011_22_finemapping.xlsx
+++ b/A/chrII:526178-574011_22_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3382" uniqueCount="3382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3374" uniqueCount="3374">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">7/13</t>
   </si>
   <si>
-    <t xml:space="preserve">311/1932</t>
+    <t xml:space="preserve">318/1932</t>
   </si>
   <si>
     <t xml:space="preserve">YAL038W/YGR248W/YHR174W/YKL060C/YLR044C/YMR105C/YOR374W</t>
@@ -9422,19 +9422,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -9675,21 +9666,6 @@
   </si>
   <si>
     <t xml:space="preserve">YMR196W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -10596,48 +10572,42 @@
         <v>3132</v>
       </c>
       <c r="Z1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3133</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3134</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3135</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3136</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3137</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3138</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3139</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3140</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3141</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3142</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -10691,59 +10661,57 @@
         <v>571411</v>
       </c>
       <c r="U2" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="V2" t="n">
         <v>71786</v>
       </c>
       <c r="W2" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.0404013248960149</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0116477532677863</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3145</v>
       </c>
       <c r="AD2" t="s">
         <v>18</v>
       </c>
       <c r="AE2" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>3145</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="b">
+      <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>3149</v>
+      <c r="AH2" t="s">
+        <v>3146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>3150</v>
+        <v>3147</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -10797,62 +10765,60 @@
         <v>571411</v>
       </c>
       <c r="U3" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="V3" t="n">
         <v>326270</v>
       </c>
       <c r="W3" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.0344574692679983</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.00948809414070864</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3149</v>
       </c>
       <c r="AD3" t="s">
         <v>18</v>
       </c>
       <c r="AE3" t="s">
-        <v>3152</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3152</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3149</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="b">
+      <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>3153</v>
+      <c r="AH3" t="s">
+        <v>3150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>3154</v>
+        <v>3151</v>
       </c>
       <c r="D4" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="E4" t="n">
         <v>533146</v>
@@ -10903,62 +10869,60 @@
         <v>539908</v>
       </c>
       <c r="U4" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="V4" t="n">
         <v>231281</v>
       </c>
       <c r="W4" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.163578621799723</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.050078749810105</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3154</v>
       </c>
       <c r="AD4" t="s">
         <v>18</v>
       </c>
       <c r="AE4" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>3154</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" t="b">
+      <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>3158</v>
+      <c r="AH4" t="s">
+        <v>3155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>3159</v>
+        <v>3156</v>
       </c>
       <c r="D5" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="E5" t="n">
         <v>526512</v>
@@ -11009,62 +10973,60 @@
         <v>527528</v>
       </c>
       <c r="U5" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="V5" t="n">
         <v>517958</v>
       </c>
       <c r="W5" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.0677859935347266</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0218774531636253</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3159</v>
       </c>
       <c r="AD5" t="s">
         <v>18</v>
       </c>
       <c r="AE5" t="s">
-        <v>3162</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3162</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>3163</v>
+      <c r="AH5" t="s">
+        <v>3160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>3164</v>
+        <v>3161</v>
       </c>
       <c r="D6" t="s">
-        <v>3165</v>
+        <v>3162</v>
       </c>
       <c r="E6" t="n">
         <v>535995</v>
@@ -11115,62 +11077,60 @@
         <v>550142</v>
       </c>
       <c r="U6" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="V6" t="n">
         <v>599417</v>
       </c>
       <c r="W6" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.173395484877961</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0539929650405615</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3164</v>
       </c>
       <c r="AD6" t="s">
         <v>18</v>
       </c>
       <c r="AE6" t="s">
-        <v>3167</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3167</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>3164</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" t="b">
+      <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>3168</v>
+      <c r="AH6" t="s">
+        <v>3165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="D7" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="E7" t="n">
         <v>533146</v>
@@ -11221,62 +11181,60 @@
         <v>537210</v>
       </c>
       <c r="U7" t="s">
-        <v>3171</v>
+        <v>3168</v>
       </c>
       <c r="V7" t="n">
         <v>255115</v>
       </c>
       <c r="W7" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.0547980861316732</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0211497430710862</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3169</v>
       </c>
       <c r="AD7" t="s">
         <v>18</v>
       </c>
       <c r="AE7" t="s">
-        <v>3172</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3172</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3173</v>
+        <v>3169</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3170</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3174</v>
+        <v>3171</v>
       </c>
       <c r="D8" t="s">
-        <v>3175</v>
+        <v>3172</v>
       </c>
       <c r="E8" t="n">
         <v>517283</v>
@@ -11327,59 +11285,57 @@
         <v>573826</v>
       </c>
       <c r="U8" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="V8" t="n">
         <v>1154075</v>
       </c>
       <c r="W8" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3177</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3174</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.207516025206056</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0732781875856953</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3175</v>
       </c>
       <c r="AD8" t="s">
         <v>18</v>
       </c>
       <c r="AE8" t="s">
-        <v>3178</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3178</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>3175</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" t="b">
+      <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>3179</v>
+      <c r="AH8" t="s">
+        <v>3176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>3180</v>
+        <v>3177</v>
       </c>
       <c r="D9" t="s">
         <v>70</v>
@@ -11433,62 +11389,60 @@
         <v>542283</v>
       </c>
       <c r="U9" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="V9" t="n">
         <v>139364</v>
       </c>
       <c r="W9" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.0817594035526784</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0297517954635631</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3145</v>
       </c>
       <c r="AD9" t="s">
         <v>18</v>
       </c>
       <c r="AE9" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>3145</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" t="b">
+      <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>3181</v>
+      <c r="AH9" t="s">
+        <v>3178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>3182</v>
+        <v>3179</v>
       </c>
       <c r="D10" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="E10" t="n">
         <v>534637</v>
@@ -11539,62 +11493,60 @@
         <v>539908</v>
       </c>
       <c r="U10" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="V10" t="n">
         <v>1039840</v>
       </c>
       <c r="W10" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.107383286235835</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.041823163101927</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3154</v>
       </c>
       <c r="AD10" t="s">
         <v>18</v>
       </c>
       <c r="AE10" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>3154</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>3183</v>
+      <c r="AH10" t="s">
+        <v>3180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3184</v>
+        <v>3181</v>
       </c>
       <c r="D11" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="E11" t="n">
         <v>533146</v>
@@ -11645,59 +11597,57 @@
         <v>541108</v>
       </c>
       <c r="U11" t="s">
-        <v>3186</v>
+        <v>3183</v>
       </c>
       <c r="V11" t="n">
         <v>571157</v>
       </c>
       <c r="W11" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.198012135697781</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0866286756289858</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3184</v>
       </c>
       <c r="AD11" t="s">
         <v>18</v>
       </c>
       <c r="AE11" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>3184</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" t="b">
+      <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>3188</v>
+      <c r="AH11" t="s">
+        <v>3185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>3189</v>
+        <v>3186</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -11751,62 +11701,60 @@
         <v>571411</v>
       </c>
       <c r="U12" t="s">
-        <v>3190</v>
+        <v>3187</v>
       </c>
       <c r="V12" t="n">
         <v>451327</v>
       </c>
       <c r="W12" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.0292001471276423</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.011270960510991</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3188</v>
       </c>
       <c r="AD12" t="s">
         <v>18</v>
       </c>
       <c r="AE12" t="s">
-        <v>3191</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3191</v>
-      </c>
-      <c r="AH12" t="n">
+        <v>3188</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" t="b">
+      <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>3192</v>
+      <c r="AH12" t="s">
+        <v>3189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
       <c r="D13" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="E13" t="n">
         <v>533767</v>
@@ -11857,62 +11805,60 @@
         <v>537210</v>
       </c>
       <c r="U13" t="s">
-        <v>3194</v>
+        <v>3191</v>
       </c>
       <c r="V13" t="n">
         <v>232285</v>
       </c>
       <c r="W13" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.0266577090642849</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.00997291717875194</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3192</v>
       </c>
       <c r="AD13" t="s">
         <v>18</v>
       </c>
       <c r="AE13" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>3192</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>3196</v>
+      <c r="AH13" t="s">
+        <v>3193</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>3197</v>
+        <v>3194</v>
       </c>
       <c r="D14" t="s">
-        <v>3198</v>
+        <v>3195</v>
       </c>
       <c r="E14" t="n">
         <v>533146</v>
@@ -11963,59 +11909,57 @@
         <v>550847</v>
       </c>
       <c r="U14" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="V14" t="n">
         <v>20978</v>
       </c>
       <c r="W14" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.0397592970367831</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0148857493854052</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3164</v>
       </c>
       <c r="AD14" t="s">
         <v>18</v>
       </c>
       <c r="AE14" t="s">
-        <v>3167</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3167</v>
-      </c>
-      <c r="AH14" t="n">
+        <v>3164</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" t="b">
+      <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>3199</v>
+      <c r="AH14" t="s">
+        <v>3196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>3200</v>
+        <v>3197</v>
       </c>
       <c r="D15" t="s">
         <v>90</v>
@@ -12069,62 +12013,60 @@
         <v>560987</v>
       </c>
       <c r="U15" t="s">
-        <v>3194</v>
+        <v>3191</v>
       </c>
       <c r="V15" t="n">
         <v>95445</v>
       </c>
       <c r="W15" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.0572663564932589</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0226994533155351</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3192</v>
       </c>
       <c r="AD15" t="s">
         <v>18</v>
       </c>
       <c r="AE15" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>3192</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>3201</v>
+      <c r="AH15" t="s">
+        <v>3198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>3202</v>
+        <v>3199</v>
       </c>
       <c r="D16" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="E16" t="n">
         <v>533146</v>
@@ -12175,62 +12117,60 @@
         <v>537210</v>
       </c>
       <c r="U16" t="s">
-        <v>3186</v>
+        <v>3183</v>
       </c>
       <c r="V16" t="n">
         <v>475769</v>
       </c>
       <c r="W16" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.122495303189479</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0493036749600031</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3184</v>
       </c>
       <c r="AD16" t="s">
         <v>18</v>
       </c>
       <c r="AE16" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>3184</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>3203</v>
+      <c r="AH16" t="s">
+        <v>3200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>3204</v>
+        <v>3201</v>
       </c>
       <c r="D17" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="E17" t="n">
         <v>406787</v>
@@ -12281,62 +12221,60 @@
         <v>541108</v>
       </c>
       <c r="U17" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="V17" t="n">
         <v>1059531</v>
       </c>
       <c r="W17" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.0197352385233743</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.00809273946045374</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3154</v>
       </c>
       <c r="AD17" t="s">
         <v>18</v>
       </c>
       <c r="AE17" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>3154</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" t="b">
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>3205</v>
+      <c r="AH17" t="s">
+        <v>3202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>3206</v>
+        <v>3203</v>
       </c>
       <c r="D18" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="E18" t="n">
         <v>533146</v>
@@ -12387,59 +12325,57 @@
         <v>537210</v>
       </c>
       <c r="U18" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="V18" t="n">
         <v>44065</v>
       </c>
       <c r="W18" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.0419702294766417</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0176796385866752</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3175</v>
       </c>
       <c r="AD18" t="s">
         <v>18</v>
       </c>
       <c r="AE18" t="s">
-        <v>3178</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3178</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3175</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>3207</v>
+      <c r="AH18" t="s">
+        <v>3204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>3208</v>
+        <v>3205</v>
       </c>
       <c r="D19" t="s">
         <v>71</v>
@@ -12493,62 +12429,60 @@
         <v>545558</v>
       </c>
       <c r="U19" t="s">
-        <v>3194</v>
+        <v>3191</v>
       </c>
       <c r="V19" t="n">
         <v>903066</v>
       </c>
       <c r="W19" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.196221150847723</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0863350916805357</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3192</v>
       </c>
       <c r="AD19" t="s">
         <v>18</v>
       </c>
       <c r="AE19" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>3192</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>3209</v>
+      <c r="AH19" t="s">
+        <v>3206</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>3210</v>
+        <v>3207</v>
       </c>
       <c r="D20" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="E20" t="n">
         <v>526512</v>
@@ -12599,62 +12533,60 @@
         <v>537210</v>
       </c>
       <c r="U20" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="V20" t="n">
         <v>985972</v>
       </c>
       <c r="W20" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-0.162238453800779</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0775105206324309</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3164</v>
       </c>
       <c r="AD20" t="s">
         <v>18</v>
       </c>
       <c r="AE20" t="s">
-        <v>3167</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3167</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>3164</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>3211</v>
+      <c r="AH20" t="s">
+        <v>3208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>3212</v>
+        <v>3209</v>
       </c>
       <c r="D21" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="E21" t="n">
         <v>526512</v>
@@ -12705,62 +12637,60 @@
         <v>541108</v>
       </c>
       <c r="U21" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="V21" t="n">
         <v>1385176</v>
       </c>
       <c r="W21" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.0825143152009764</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.048701254548792</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3175</v>
       </c>
       <c r="AD21" t="s">
         <v>18</v>
       </c>
       <c r="AE21" t="s">
-        <v>3178</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3178</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>3175</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2</v>
       </c>
-      <c r="AI21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>3213</v>
+      <c r="AG21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>3210</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>3214</v>
+        <v>3211</v>
       </c>
       <c r="D22" t="s">
-        <v>3215</v>
+        <v>3212</v>
       </c>
       <c r="E22" t="n">
         <v>565250</v>
@@ -12811,62 +12741,60 @@
         <v>565460</v>
       </c>
       <c r="U22" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="V22" t="n">
         <v>1069501</v>
       </c>
       <c r="W22" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.00951768970013968</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0695334977049957</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3154</v>
       </c>
       <c r="AD22" t="s">
         <v>18</v>
       </c>
       <c r="AE22" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3157</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>3154</v>
+      </c>
+      <c r="AF22" t="n">
         <v>4</v>
       </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>3214</v>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>3211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>3216</v>
+        <v>3213</v>
       </c>
       <c r="D23" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="E23" t="n">
         <v>513451</v>
@@ -12917,48 +12845,46 @@
         <v>527528</v>
       </c>
       <c r="U23" t="s">
-        <v>3186</v>
+        <v>3183</v>
       </c>
       <c r="V23" t="n">
         <v>655076</v>
       </c>
       <c r="W23" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3147</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3144</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.183995899091755</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0834267968991522</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3184</v>
       </c>
       <c r="AD23" t="s">
         <v>18</v>
       </c>
       <c r="AE23" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3184</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>3216</v>
+      <c r="AH23" t="s">
+        <v>3213</v>
       </c>
     </row>
   </sheetData>
@@ -13037,37 +12963,28 @@
         <v>3129</v>
       </c>
       <c r="V1" t="s">
-        <v>3217</v>
+        <v>40</v>
       </c>
       <c r="W1" t="s">
-        <v>3218</v>
+        <v>3133</v>
       </c>
       <c r="X1" t="s">
-        <v>3219</v>
+        <v>3134</v>
       </c>
       <c r="Y1" t="s">
-        <v>3220</v>
+        <v>3135</v>
       </c>
       <c r="Z1" t="s">
-        <v>3221</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="AB1" t="s">
-        <v>3138</v>
+        <v>3214</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3139</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3222</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3142</v>
       </c>
     </row>
     <row r="2">
@@ -13075,10 +12992,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="C2" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
       <c r="D2" t="n">
         <v>559732</v>
@@ -13135,37 +13052,28 @@
         <v>558685</v>
       </c>
       <c r="V2" t="n">
-        <v>-8.2041886258401</v>
+        <v>-0.360442503115397</v>
       </c>
       <c r="W2" t="n">
-        <v>-5.01049982770716</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-5.57855073180101</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-6.26458157812757</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-5.90525697731598</v>
+        <v>0.0573452961501891</v>
+      </c>
+      <c r="X2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>18</v>
       </c>
       <c r="AA2" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" t="s">
-        <v>18</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3225</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="3">
@@ -13173,10 +13081,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="C3" t="s">
-        <v>3224</v>
+        <v>3216</v>
       </c>
       <c r="D3" t="n">
         <v>550142</v>
@@ -13233,37 +13141,28 @@
         <v>553423</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.28263966334991</v>
+        <v>-0.500708231573914</v>
       </c>
       <c r="W3" t="n">
-        <v>-4.31336929784663</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-6.15471591948512</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1.539842137127</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.97026932925331</v>
+        <v>0.110860396560424</v>
+      </c>
+      <c r="X3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>18</v>
       </c>
       <c r="AA3" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" t="s">
-        <v>18</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3227</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="4">
@@ -13271,10 +13170,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
       <c r="C4" t="s">
-        <v>3229</v>
+        <v>3221</v>
       </c>
       <c r="D4" t="n">
         <v>559732</v>
@@ -13331,37 +13230,28 @@
         <v>576185</v>
       </c>
       <c r="V4" t="n">
-        <v>4.49506685380369</v>
+        <v>0.134438927027425</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6847126186112</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.08300223207885</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.881459627902735</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.917927958807758</v>
+        <v>0.0705123899368041</v>
+      </c>
+      <c r="X4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>18</v>
       </c>
       <c r="AA4" t="s">
         <v>18</v>
       </c>
-      <c r="AB4" t="s">
-        <v>18</v>
+      <c r="AB4" t="n">
+        <v>0.000403225806451613</v>
       </c>
       <c r="AC4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.000403225806451613</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3230</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="5">
@@ -13369,7 +13259,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
@@ -13429,37 +13319,28 @@
         <v>530749</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.86572642324748</v>
+        <v>-0.0564208109448678</v>
       </c>
       <c r="W5" t="n">
-        <v>-3.34103058219919</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.48601621834759</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-3.13302359917421</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.792970035026777</v>
+        <v>0.0268172059824416</v>
+      </c>
+      <c r="X5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>18</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>
       </c>
-      <c r="AB5" t="s">
-        <v>18</v>
+      <c r="AB5" t="n">
+        <v>0.000403225806451613</v>
       </c>
       <c r="AC5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.000403225806451613</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3232</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="6">
@@ -13467,10 +13348,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="C6" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="D6" t="n">
         <v>459672</v>
@@ -13527,37 +13408,28 @@
         <v>528317</v>
       </c>
       <c r="V6" t="n">
-        <v>3.69539183581461</v>
+        <v>0.186900398194854</v>
       </c>
       <c r="W6" t="n">
-        <v>2.37188618566587</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.191255606167248</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.13872756249188</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.75074323600489</v>
+        <v>0.0951902077289088</v>
+      </c>
+      <c r="X6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>18</v>
       </c>
       <c r="AA6" t="s">
         <v>18</v>
       </c>
-      <c r="AB6" t="s">
-        <v>18</v>
+      <c r="AB6" t="n">
+        <v>0.00065359477124183</v>
       </c>
       <c r="AC6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.00065359477124183</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="7">
@@ -13565,10 +13437,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="C7" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="D7" t="n">
         <v>378868</v>
@@ -13625,37 +13497,28 @@
         <v>578364</v>
       </c>
       <c r="V7" t="n">
-        <v>3.01358413624608</v>
+        <v>0.0417662468914323</v>
       </c>
       <c r="W7" t="n">
-        <v>0.669692936397141</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.62583050794204</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.75532294968709</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.438290014544668</v>
+        <v>0.0360296847893969</v>
+      </c>
+      <c r="X7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>18</v>
       </c>
       <c r="AA7" t="s">
         <v>18</v>
       </c>
-      <c r="AB7" t="s">
-        <v>18</v>
+      <c r="AB7" t="n">
+        <v>0.00671140939597315</v>
       </c>
       <c r="AC7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.00671140939597315</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="8">
@@ -13663,10 +13526,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="C8" t="s">
-        <v>3165</v>
+        <v>3162</v>
       </c>
       <c r="D8" t="n">
         <v>480340</v>
@@ -13723,37 +13586,28 @@
         <v>550984</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.95812360989341</v>
+        <v>-0.0851314163356098</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.61110891006932</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.01171628964071</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.0105052514187378</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.66808886542657</v>
+        <v>0.139299321910991</v>
+      </c>
+      <c r="X8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>18</v>
       </c>
       <c r="AA8" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" t="s">
-        <v>18</v>
+      <c r="AB8" t="n">
+        <v>0.0107769423558897</v>
       </c>
       <c r="AC8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.0107769423558897</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="9">
@@ -13761,10 +13615,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="C9" t="s">
-        <v>3242</v>
+        <v>3234</v>
       </c>
       <c r="D9" t="n">
         <v>274614</v>
@@ -13821,37 +13675,28 @@
         <v>579013</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.918986358636546</v>
+        <v>-0.0378279007047843</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.81298491274382</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.277569817731507</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.74589422397572</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.30085948935455</v>
+        <v>0.0637453781815288</v>
+      </c>
+      <c r="X9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>18</v>
       </c>
       <c r="AA9" t="s">
         <v>18</v>
       </c>
-      <c r="AB9" t="s">
-        <v>18</v>
+      <c r="AB9" t="n">
+        <v>0.0147457248702096</v>
       </c>
       <c r="AC9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.0147457248702096</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="10">
@@ -13859,10 +13704,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="C10" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="D10" t="n">
         <v>35660</v>
@@ -13919,37 +13764,28 @@
         <v>568852</v>
       </c>
       <c r="V10" t="n">
-        <v>3.15358127292966</v>
+        <v>0.108831535021151</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22898163348646</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.19801884865126</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.72472784641905</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.0993335775315629</v>
+        <v>0.0704427556408901</v>
+      </c>
+      <c r="X10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>18</v>
       </c>
       <c r="AA10" t="s">
         <v>18</v>
       </c>
-      <c r="AB10" t="s">
-        <v>18</v>
+      <c r="AB10" t="n">
+        <v>0.0306008042566641</v>
       </c>
       <c r="AC10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.0306008042566641</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="11">
@@ -13957,10 +13793,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="C11" t="s">
-        <v>3248</v>
+        <v>3240</v>
       </c>
       <c r="D11" t="n">
         <v>502627</v>
@@ -14017,37 +13853,28 @@
         <v>569754</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.42956680570321</v>
+        <v>-0.136712348362765</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.59896279983476</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-2.70133783572579</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-1.98811473394172</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-1.47919003871393</v>
+        <v>0.0847667968313544</v>
+      </c>
+      <c r="X11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>18</v>
       </c>
       <c r="AA11" t="s">
         <v>18</v>
       </c>
-      <c r="AB11" t="s">
-        <v>18</v>
+      <c r="AB11" t="n">
+        <v>0.0307855626326964</v>
       </c>
       <c r="AC11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.0307855626326964</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
     </row>
   </sheetData>
@@ -14078,34 +13905,34 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>3250</v>
+        <v>3242</v>
       </c>
       <c r="G1" t="s">
         <v>1595</v>
       </c>
       <c r="H1" t="s">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="I1" t="s">
-        <v>3252</v>
+        <v>3244</v>
       </c>
       <c r="J1" t="s">
         <v>1609</v>
       </c>
       <c r="K1" t="s">
-        <v>3253</v>
+        <v>3245</v>
       </c>
       <c r="L1" t="s">
-        <v>3254</v>
+        <v>3246</v>
       </c>
       <c r="M1" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="N1" t="s">
-        <v>3256</v>
+        <v>3248</v>
       </c>
       <c r="O1" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="P1" t="s">
         <v>3129</v>
@@ -14125,30 +13952,30 @@
         <v>1527</v>
       </c>
       <c r="E2" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F2" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G2" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
       <c r="K2" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="L2" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
       <c r="M2" t="s">
-        <v>3262</v>
+        <v>3254</v>
       </c>
       <c r="N2" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O2"/>
       <c r="P2" t="n">
@@ -14169,33 +13996,33 @@
         <v>9279</v>
       </c>
       <c r="E3" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F3" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G3" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="K3" t="s">
-        <v>3266</v>
+        <v>3258</v>
       </c>
       <c r="L3" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="M3" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="N3" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O3" t="s">
-        <v>3268</v>
+        <v>3260</v>
       </c>
       <c r="P3" t="n">
         <v>521989</v>
@@ -14215,33 +14042,33 @@
         <v>1014</v>
       </c>
       <c r="E4" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F4" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G4" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3269</v>
+        <v>3261</v>
       </c>
       <c r="K4" t="s">
-        <v>3270</v>
+        <v>3262</v>
       </c>
       <c r="L4" t="s">
-        <v>3269</v>
+        <v>3261</v>
       </c>
       <c r="M4" t="s">
-        <v>3271</v>
+        <v>3263</v>
       </c>
       <c r="N4" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O4" t="s">
-        <v>3272</v>
+        <v>3264</v>
       </c>
       <c r="P4" t="n">
         <v>527532</v>
@@ -14261,33 +14088,33 @@
         <v>2322</v>
       </c>
       <c r="E5" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F5" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G5" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="K5" t="s">
-        <v>3273</v>
+        <v>3265</v>
       </c>
       <c r="L5" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="M5" t="s">
-        <v>3274</v>
+        <v>3266</v>
       </c>
       <c r="N5" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O5" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="P5" t="n">
         <v>529478</v>
@@ -14307,33 +14134,33 @@
         <v>1314</v>
       </c>
       <c r="E6" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F6" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G6" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="K6" t="s">
-        <v>3275</v>
+        <v>3267</v>
       </c>
       <c r="L6" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="M6" t="s">
-        <v>3276</v>
+        <v>3268</v>
       </c>
       <c r="N6" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O6" t="s">
-        <v>3232</v>
+        <v>3224</v>
       </c>
       <c r="P6" t="n">
         <v>531526</v>
@@ -14353,30 +14180,30 @@
         <v>315</v>
       </c>
       <c r="E7" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F7" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G7" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3277</v>
+        <v>3269</v>
       </c>
       <c r="K7" t="s">
-        <v>3278</v>
+        <v>3270</v>
       </c>
       <c r="L7" t="s">
-        <v>3277</v>
+        <v>3269</v>
       </c>
       <c r="M7" t="s">
-        <v>3279</v>
+        <v>3271</v>
       </c>
       <c r="N7" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
@@ -14397,33 +14224,33 @@
         <v>1056</v>
       </c>
       <c r="E8" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F8" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G8" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="K8" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="L8" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="M8" t="s">
-        <v>3283</v>
+        <v>3275</v>
       </c>
       <c r="N8" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O8" t="s">
-        <v>3284</v>
+        <v>3276</v>
       </c>
       <c r="P8" t="n">
         <v>534290</v>
@@ -14443,33 +14270,33 @@
         <v>837</v>
       </c>
       <c r="E9" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F9" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G9" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3285</v>
+        <v>3277</v>
       </c>
       <c r="K9" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="L9" t="s">
-        <v>3285</v>
+        <v>3277</v>
       </c>
       <c r="M9" t="s">
-        <v>3287</v>
+        <v>3279</v>
       </c>
       <c r="N9" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O9" t="s">
-        <v>3288</v>
+        <v>3280</v>
       </c>
       <c r="P9" t="n">
         <v>535678</v>
@@ -14489,33 +14316,33 @@
         <v>891</v>
       </c>
       <c r="E10" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F10" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G10" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="K10" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="L10" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="M10" t="s">
-        <v>3291</v>
+        <v>3283</v>
       </c>
       <c r="N10" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O10" t="s">
-        <v>3292</v>
+        <v>3284</v>
       </c>
       <c r="P10" t="n">
         <v>537020</v>
@@ -14535,33 +14362,33 @@
         <v>1830</v>
       </c>
       <c r="E11" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F11" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G11" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3293</v>
+        <v>3285</v>
       </c>
       <c r="K11" t="s">
-        <v>3294</v>
+        <v>3286</v>
       </c>
       <c r="L11" t="s">
-        <v>3293</v>
+        <v>3285</v>
       </c>
       <c r="M11" t="s">
-        <v>3295</v>
+        <v>3287</v>
       </c>
       <c r="N11" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O11" t="s">
-        <v>3296</v>
+        <v>3288</v>
       </c>
       <c r="P11" t="n">
         <v>538790</v>
@@ -14581,33 +14408,33 @@
         <v>1035</v>
       </c>
       <c r="E12" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F12" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G12" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3297</v>
+        <v>3289</v>
       </c>
       <c r="K12" t="s">
-        <v>3298</v>
+        <v>3290</v>
       </c>
       <c r="L12" t="s">
-        <v>3297</v>
+        <v>3289</v>
       </c>
       <c r="M12" t="s">
-        <v>3299</v>
+        <v>3291</v>
       </c>
       <c r="N12" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O12" t="s">
-        <v>3300</v>
+        <v>3292</v>
       </c>
       <c r="P12" t="n">
         <v>540504</v>
@@ -14627,33 +14454,33 @@
         <v>3285</v>
       </c>
       <c r="E13" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F13" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G13" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3301</v>
+        <v>3293</v>
       </c>
       <c r="K13" t="s">
-        <v>3302</v>
+        <v>3294</v>
       </c>
       <c r="L13" t="s">
-        <v>3301</v>
+        <v>3293</v>
       </c>
       <c r="M13" t="s">
-        <v>3303</v>
+        <v>3295</v>
       </c>
       <c r="N13" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O13" t="s">
-        <v>3304</v>
+        <v>3296</v>
       </c>
       <c r="P13" t="n">
         <v>542851</v>
@@ -14673,33 +14500,33 @@
         <v>951</v>
       </c>
       <c r="E14" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F14" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G14" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3305</v>
+        <v>3297</v>
       </c>
       <c r="K14" t="s">
-        <v>3306</v>
+        <v>3298</v>
       </c>
       <c r="L14" t="s">
-        <v>3305</v>
+        <v>3297</v>
       </c>
       <c r="M14" t="s">
-        <v>3303</v>
+        <v>3295</v>
       </c>
       <c r="N14" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O14" t="s">
-        <v>3307</v>
+        <v>3299</v>
       </c>
       <c r="P14" t="n">
         <v>545503</v>
@@ -14719,33 +14546,33 @@
         <v>876</v>
       </c>
       <c r="E15" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F15" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G15" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3308</v>
+        <v>3300</v>
       </c>
       <c r="K15" t="s">
-        <v>3309</v>
+        <v>3301</v>
       </c>
       <c r="L15" t="s">
-        <v>3308</v>
+        <v>3300</v>
       </c>
       <c r="M15" t="s">
-        <v>3310</v>
+        <v>3302</v>
       </c>
       <c r="N15" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O15" t="s">
-        <v>3311</v>
+        <v>3303</v>
       </c>
       <c r="P15" t="n">
         <v>546814</v>
@@ -14765,33 +14592,33 @@
         <v>735</v>
       </c>
       <c r="E16" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F16" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G16" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3312</v>
+        <v>3304</v>
       </c>
       <c r="K16" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="L16" t="s">
-        <v>3312</v>
+        <v>3304</v>
       </c>
       <c r="M16" t="s">
-        <v>3314</v>
+        <v>3306</v>
       </c>
       <c r="N16" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O16" t="s">
-        <v>3315</v>
+        <v>3307</v>
       </c>
       <c r="P16" t="n">
         <v>547827</v>
@@ -14811,33 +14638,33 @@
         <v>648</v>
       </c>
       <c r="E17" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F17" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G17" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3316</v>
+        <v>3308</v>
       </c>
       <c r="K17" t="s">
-        <v>3317</v>
+        <v>3309</v>
       </c>
       <c r="L17" t="s">
-        <v>3316</v>
+        <v>3308</v>
       </c>
       <c r="M17" t="s">
-        <v>3318</v>
+        <v>3310</v>
       </c>
       <c r="N17" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O17" t="s">
-        <v>3319</v>
+        <v>3311</v>
       </c>
       <c r="P17" t="n">
         <v>548686</v>
@@ -14857,33 +14684,33 @@
         <v>1158</v>
       </c>
       <c r="E18" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F18" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G18" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3320</v>
+        <v>3312</v>
       </c>
       <c r="K18" t="s">
-        <v>3321</v>
+        <v>3313</v>
       </c>
       <c r="L18" t="s">
-        <v>3320</v>
+        <v>3312</v>
       </c>
       <c r="M18" t="s">
-        <v>3322</v>
+        <v>3314</v>
       </c>
       <c r="N18" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O18" t="s">
-        <v>3323</v>
+        <v>3315</v>
       </c>
       <c r="P18" t="n">
         <v>550350</v>
@@ -14903,33 +14730,33 @@
         <v>2097</v>
       </c>
       <c r="E19" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F19" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G19" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="K19" t="s">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="L19" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="M19" t="s">
-        <v>3325</v>
+        <v>3317</v>
       </c>
       <c r="N19" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O19" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="P19" t="n">
         <v>552152</v>
@@ -14949,33 +14776,33 @@
         <v>768</v>
       </c>
       <c r="E20" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F20" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G20" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="K20" t="s">
-        <v>3326</v>
+        <v>3318</v>
       </c>
       <c r="L20" t="s">
-        <v>3226</v>
+        <v>3218</v>
       </c>
       <c r="M20" t="s">
-        <v>3303</v>
+        <v>3295</v>
       </c>
       <c r="N20" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O20" t="s">
-        <v>3227</v>
+        <v>3219</v>
       </c>
       <c r="P20" t="n">
         <v>553926</v>
@@ -14995,33 +14822,33 @@
         <v>1650</v>
       </c>
       <c r="E21" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F21" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G21" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3327</v>
+        <v>3319</v>
       </c>
       <c r="K21" t="s">
-        <v>3328</v>
+        <v>3320</v>
       </c>
       <c r="L21" t="s">
-        <v>3327</v>
+        <v>3319</v>
       </c>
       <c r="M21" t="s">
-        <v>3329</v>
+        <v>3321</v>
       </c>
       <c r="N21" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O21" t="s">
-        <v>3330</v>
+        <v>3322</v>
       </c>
       <c r="P21" t="n">
         <v>557374</v>
@@ -15041,33 +14868,33 @@
         <v>1044</v>
       </c>
       <c r="E22" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F22" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G22" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="K22" t="s">
-        <v>3331</v>
+        <v>3323</v>
       </c>
       <c r="L22" t="s">
-        <v>3223</v>
+        <v>3215</v>
       </c>
       <c r="M22" t="s">
-        <v>3332</v>
+        <v>3324</v>
       </c>
       <c r="N22" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O22" t="s">
-        <v>3225</v>
+        <v>3217</v>
       </c>
       <c r="P22" t="n">
         <v>559206</v>
@@ -15087,33 +14914,33 @@
         <v>897</v>
       </c>
       <c r="E23" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F23" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G23" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3333</v>
+        <v>3325</v>
       </c>
       <c r="K23" t="s">
-        <v>3334</v>
+        <v>3326</v>
       </c>
       <c r="L23" t="s">
-        <v>3333</v>
+        <v>3325</v>
       </c>
       <c r="M23" t="s">
-        <v>3335</v>
+        <v>3327</v>
       </c>
       <c r="N23" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O23" t="s">
-        <v>3336</v>
+        <v>3328</v>
       </c>
       <c r="P23" t="n">
         <v>560526</v>
@@ -15133,33 +14960,33 @@
         <v>1131</v>
       </c>
       <c r="E24" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F24" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G24" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3337</v>
+        <v>3329</v>
       </c>
       <c r="K24" t="s">
-        <v>3338</v>
+        <v>3330</v>
       </c>
       <c r="L24" t="s">
-        <v>3337</v>
+        <v>3329</v>
       </c>
       <c r="M24" t="s">
-        <v>3339</v>
+        <v>3331</v>
       </c>
       <c r="N24" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O24" t="s">
-        <v>3340</v>
+        <v>3332</v>
       </c>
       <c r="P24" t="n">
         <v>562199</v>
@@ -15179,33 +15006,33 @@
         <v>1368</v>
       </c>
       <c r="E25" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F25" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G25" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3341</v>
+        <v>3333</v>
       </c>
       <c r="K25" t="s">
-        <v>3342</v>
+        <v>3334</v>
       </c>
       <c r="L25" t="s">
-        <v>3341</v>
+        <v>3333</v>
       </c>
       <c r="M25" t="s">
-        <v>3343</v>
+        <v>3335</v>
       </c>
       <c r="N25" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O25" t="s">
-        <v>3344</v>
+        <v>3336</v>
       </c>
       <c r="P25" t="n">
         <v>563886</v>
@@ -15225,33 +15052,33 @@
         <v>198</v>
       </c>
       <c r="E26" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F26" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G26" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3345</v>
+        <v>3337</v>
       </c>
       <c r="K26" t="s">
-        <v>3346</v>
+        <v>3338</v>
       </c>
       <c r="L26" t="s">
-        <v>3345</v>
+        <v>3337</v>
       </c>
       <c r="M26" t="s">
-        <v>3303</v>
+        <v>3295</v>
       </c>
       <c r="N26" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O26" t="s">
-        <v>3347</v>
+        <v>3339</v>
       </c>
       <c r="P26" t="n">
         <v>565330</v>
@@ -15271,33 +15098,33 @@
         <v>1758</v>
       </c>
       <c r="E27" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F27" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G27" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3348</v>
+        <v>3340</v>
       </c>
       <c r="K27" t="s">
-        <v>3349</v>
+        <v>3341</v>
       </c>
       <c r="L27" t="s">
-        <v>3348</v>
+        <v>3340</v>
       </c>
       <c r="M27" t="s">
-        <v>3350</v>
+        <v>3342</v>
       </c>
       <c r="N27" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O27" t="s">
-        <v>3351</v>
+        <v>3343</v>
       </c>
       <c r="P27" t="n">
         <v>566602</v>
@@ -15317,33 +15144,33 @@
         <v>552</v>
       </c>
       <c r="E28" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F28" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G28" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3352</v>
+        <v>3344</v>
       </c>
       <c r="K28" t="s">
-        <v>3353</v>
+        <v>3345</v>
       </c>
       <c r="L28" t="s">
-        <v>3352</v>
+        <v>3344</v>
       </c>
       <c r="M28" t="s">
-        <v>3354</v>
+        <v>3346</v>
       </c>
       <c r="N28" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O28" t="s">
-        <v>3355</v>
+        <v>3347</v>
       </c>
       <c r="P28" t="n">
         <v>568150</v>
@@ -15363,33 +15190,33 @@
         <v>834</v>
       </c>
       <c r="E29" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F29" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G29" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="K29" t="s">
-        <v>3356</v>
+        <v>3348</v>
       </c>
       <c r="L29" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="M29" t="s">
-        <v>3357</v>
+        <v>3349</v>
       </c>
       <c r="N29" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O29" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
       <c r="P29" t="n">
         <v>569268</v>
@@ -15409,33 +15236,33 @@
         <v>1359</v>
       </c>
       <c r="E30" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F30" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G30" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="K30" t="s">
-        <v>3358</v>
+        <v>3350</v>
       </c>
       <c r="L30" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="M30" t="s">
-        <v>3359</v>
+        <v>3351</v>
       </c>
       <c r="N30" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O30" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
       <c r="P30" t="n">
         <v>570521</v>
@@ -15455,33 +15282,33 @@
         <v>423</v>
       </c>
       <c r="E31" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F31" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G31" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>3360</v>
+        <v>3352</v>
       </c>
       <c r="K31" t="s">
-        <v>3361</v>
+        <v>3353</v>
       </c>
       <c r="L31" t="s">
-        <v>3360</v>
+        <v>3352</v>
       </c>
       <c r="M31" t="s">
-        <v>3362</v>
+        <v>3354</v>
       </c>
       <c r="N31" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O31" t="s">
-        <v>3363</v>
+        <v>3355</v>
       </c>
       <c r="P31" t="n">
         <v>571679</v>
@@ -15501,33 +15328,33 @@
         <v>1242</v>
       </c>
       <c r="E32" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F32" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G32" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>3364</v>
+        <v>3356</v>
       </c>
       <c r="K32" t="s">
-        <v>3365</v>
+        <v>3357</v>
       </c>
       <c r="L32" t="s">
-        <v>3364</v>
+        <v>3356</v>
       </c>
       <c r="M32" t="s">
-        <v>3366</v>
+        <v>3358</v>
       </c>
       <c r="N32" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O32" t="s">
-        <v>3367</v>
+        <v>3359</v>
       </c>
       <c r="P32" t="n">
         <v>572992</v>
@@ -15547,33 +15374,33 @@
         <v>2082</v>
       </c>
       <c r="E33" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F33" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G33" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>3368</v>
+        <v>3360</v>
       </c>
       <c r="K33" t="s">
-        <v>3369</v>
+        <v>3361</v>
       </c>
       <c r="L33" t="s">
-        <v>3368</v>
+        <v>3360</v>
       </c>
       <c r="M33" t="s">
-        <v>3370</v>
+        <v>3362</v>
       </c>
       <c r="N33" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O33" t="s">
-        <v>3371</v>
+        <v>3363</v>
       </c>
       <c r="P33" t="n">
         <v>574956</v>
@@ -15593,33 +15420,33 @@
         <v>1743</v>
       </c>
       <c r="E34" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F34" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G34" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
       <c r="K34" t="s">
-        <v>3372</v>
+        <v>3364</v>
       </c>
       <c r="L34" t="s">
-        <v>3228</v>
+        <v>3220</v>
       </c>
       <c r="M34" t="s">
-        <v>3373</v>
+        <v>3365</v>
       </c>
       <c r="N34" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O34" t="s">
-        <v>3230</v>
+        <v>3222</v>
       </c>
       <c r="P34" t="n">
         <v>577215</v>
@@ -15639,33 +15466,33 @@
         <v>621</v>
       </c>
       <c r="E35" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F35" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G35" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="K35" t="s">
-        <v>3374</v>
+        <v>3366</v>
       </c>
       <c r="L35" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="M35" t="s">
-        <v>3375</v>
+        <v>3367</v>
       </c>
       <c r="N35" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O35" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
       <c r="P35" t="n">
         <v>578674</v>
@@ -15685,33 +15512,33 @@
         <v>2223</v>
       </c>
       <c r="E36" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F36" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G36" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="K36" t="s">
-        <v>3376</v>
+        <v>3368</v>
       </c>
       <c r="L36" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="M36" t="s">
-        <v>3377</v>
+        <v>3369</v>
       </c>
       <c r="N36" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O36" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="P36" t="n">
         <v>580261</v>
@@ -15731,33 +15558,33 @@
         <v>447</v>
       </c>
       <c r="E37" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="F37" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G37" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>3378</v>
+        <v>3370</v>
       </c>
       <c r="K37" t="s">
-        <v>3379</v>
+        <v>3371</v>
       </c>
       <c r="L37" t="s">
-        <v>3378</v>
+        <v>3370</v>
       </c>
       <c r="M37" t="s">
-        <v>3380</v>
+        <v>3372</v>
       </c>
       <c r="N37" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O37" t="s">
-        <v>3381</v>
+        <v>3373</v>
       </c>
       <c r="P37" t="n">
         <v>581949</v>
@@ -52481,10 +52308,10 @@
         <v>0.000000172518269506497</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00000534806635470141</v>
+        <v>0.00000552058462420791</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00000345036539012994</v>
+        <v>0.00000363196356855783</v>
       </c>
       <c r="J2" t="s">
         <v>1624</v>
@@ -52516,10 +52343,10 @@
         <v>0.000340802167968665</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0052824336035143</v>
+        <v>0.00545283468749863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00340802167968665</v>
+        <v>0.00358739124177542</v>
       </c>
       <c r="J3" t="s">
         <v>1629</v>
@@ -52551,10 +52378,10 @@
         <v>0.0014959049133723</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0144900876349444</v>
+        <v>0.0159563190759712</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009348443635448</v>
+        <v>0.0104975783394547</v>
       </c>
       <c r="J4" t="s">
         <v>1635</v>
@@ -52583,13 +52410,13 @@
         <v>1640</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0018696887270896</v>
+        <v>0.00214088423766612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0144900876349444</v>
+        <v>0.017127073901329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009348443635448</v>
+        <v>0.0112678117771901</v>
       </c>
       <c r="J5" t="s">
         <v>1641</v>
@@ -52621,10 +52448,10 @@
         <v>0.00278655376743827</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0172766333581173</v>
+        <v>0.017833944111605</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0111462150697531</v>
+        <v>0.0117328579681612</v>
       </c>
       <c r="J6" t="s">
         <v>1646</v>
@@ -52656,10 +52483,10 @@
         <v>0.00670264239423398</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0346303190368756</v>
+        <v>0.0357474261025812</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0223421413141133</v>
+        <v>0.0235180434885403</v>
       </c>
       <c r="J7" t="s">
         <v>1652</v>
@@ -52691,10 +52518,10 @@
         <v>0.00926116830314365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0410137453424933</v>
+        <v>0.0423367693857995</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0264604808661247</v>
+        <v>0.0278531377538155</v>
       </c>
       <c r="J8" t="s">
         <v>1635</v>
@@ -52726,10 +52553,10 @@
         <v>0.0121394395379211</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0470403282094444</v>
+        <v>0.0485577581516846</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0303485988448029</v>
+        <v>0.0319458935208451</v>
       </c>
       <c r="J9" t="s">
         <v>1635</v>
@@ -52761,10 +52588,10 @@
         <v>0.0149806075129946</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0474940983188789</v>
+        <v>0.0490261660065846</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0306413537541154</v>
+        <v>0.0322540565832794</v>
       </c>
       <c r="J10" t="s">
         <v>1635</v>
@@ -52796,10 +52623,10 @@
         <v>0.0153206768770577</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0474940983188789</v>
+        <v>0.0490261660065846</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0306413537541154</v>
+        <v>0.0322540565832794</v>
       </c>
       <c r="J11" t="s">
         <v>1671</v>
